--- a/data/merged/2026-08-31/MERGED_UK_Stick-Vacuum_2026-08-31.xlsx
+++ b/data/merged/2026-08-31/MERGED_UK_Stick-Vacuum_2026-08-31.xlsx
@@ -4125,13 +4125,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4433,13 +4433,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4477,13 +4477,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4609,13 +4609,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4697,13 +4697,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4785,13 +4785,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4873,13 +4873,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4923,7 +4923,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4967,7 +4967,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5093,13 +5093,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5137,13 +5137,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5468,50 +5468,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5853,7 +5809,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -8184,7 +8140,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0F9YPP9C3</t>
+          <t>B0FCGB8FPQ</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -8197,23 +8153,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Shark Disposable Hard Floor Vacuum and Mop Pad VACMOP Refill 16 Pack, WhitesWhite 1304HK200UK</t>
+          <t>Shark VacMop 2-in-1 Cordless Hard Floor Vacuum Spray Mop, VM200UKGNs6x Disposable Pad Refills, 355ml Multi-Surface Floor Cl</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F9YPP9C3?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FCGB8FPQ?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61y78uO9VYL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61TKqdXibWL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0F9YPP9C3</t>
+          <t>B0FCGB8FPQ</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -8230,17 +8186,17 @@
       <c r="X20" s="15"/>
       <c r="Y20"/>
       <c r="Z20" s="4">
-        <v>12.49</v>
+        <v>58.32</v>
       </c>
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="19">
-        <v>181</v>
+        <v>544</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="20">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AG20" s="21">
         <v>0</v>
@@ -8292,7 +8248,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0FCGB8FPQ</t>
+          <t>B0FPMR4Q3T</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -8305,23 +8261,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Shark VacMop 2-in-1 Cordless Hard Floor Vacuum Spray Mop, VM200UKGNs6x Disposable Pad Refills, 355ml Multi-Surface Floor Cl</t>
+          <t>Vax HomePro Pet &amp; Car Cordless Stick Vacuum Cleaner, 45 mins, CLSV-HPKCsCordless hoover for pet hair, home &amp; car, lightweig</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FCGB8FPQ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FPMR4Q3T?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61TKqdXibWL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/610Cokti-gL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0FCGB8FPQ</t>
+          <t>B0FPMR4Q3T</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -8337,18 +8293,16 @@
       <c r="W21" s="15"/>
       <c r="X21" s="15"/>
       <c r="Y21"/>
-      <c r="Z21" s="4">
-        <v>58.32</v>
-      </c>
+      <c r="Z21" s="4"/>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="19">
-        <v>544</v>
+        <v>98</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="20">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AG21" s="21">
         <v>0</v>
@@ -8400,7 +8354,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0FPMR4Q3T</t>
+          <t>B0FT2LTJRF</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -8413,23 +8367,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Vax HomePro Pet &amp; Car Cordless Stick Vacuum Cleaner, 45 mins, CLSV-HPKCsCordless hoover for pet hair, home &amp; car, lightweig</t>
+          <t>Cordless Vacuum Cleaner 650W 55KPA, 70Mins Battery Cordless Stick VacuumsLED Touch Screen・Auto Mode・180° Foldable Wand + 1M</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FPMR4Q3T?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FT2LTJRF?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/610Cokti-gL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71amryCWm8L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0FPMR4Q3T</t>
+          <t>B0FT2LTJRF</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -8450,11 +8404,11 @@
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="19">
-        <v>98</v>
+        <v>1489</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="20">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG22" s="21">
         <v>0</v>
@@ -8506,7 +8460,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0FT2LTJRF</t>
+          <t>B0G2LVVRMJ</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -8519,23 +8473,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Cordless Vacuum Cleaner 650W 55KPA, 70Mins Battery Cordless Stick VacuumsLED Touch Screen・Auto Mode・180° Foldable Wand + 1M</t>
+          <t>VACTechPro F02 Lite Cordless Vacuum Cleaner, 40KPa/50Mins/450W Stick VacuumsSelf-Standing Anti-Tangle Upright Vacuum, Power</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FT2LTJRF?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0G2LVVRMJ?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71amryCWm8L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71gB5S-38uL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0FT2LTJRF</t>
+          <t>B0G2LVVRMJ</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -8556,7 +8510,7 @@
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="19">
-        <v>1489</v>
+        <v>644</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="20">
@@ -8612,7 +8566,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0G2LVVRMJ</t>
+          <t>B0G5Q6B3S3</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -8625,23 +8579,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>VACTechPro F02 Lite Cordless Vacuum Cleaner, 40KPa/50Mins/450W Stick VacuumsSelf-Standing Anti-Tangle Upright Vacuum, Power</t>
+          <t>Dyson Cyclone V10 Submarine Cordless Vacuum Cleaner, 150 AW, 60 min RuntimesAdvanced Cyclone Technology, Removes Pet Hair F</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0G2LVVRMJ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0G5Q6B3S3?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71gB5S-38uL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/511Z9OMUhsL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0G2LVVRMJ</t>
+          <t>B0G5Q6B3S3</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -8662,11 +8616,11 @@
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="19">
-        <v>644</v>
+        <v>44</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="20">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AG24" s="21">
         <v>0</v>
@@ -8718,7 +8672,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0G5Q6B3S3</t>
+          <t>B0G64ZJ5MQ</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -8731,23 +8685,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Dyson Cyclone V10 Submarine Cordless Vacuum Cleaner, 150 AW, 60 min RuntimesAdvanced Cyclone Technology, Removes Pet Hair F</t>
+          <t>SMOTURE Cordless Vacuum Cleaner, 55KPa 650W Stick Cordless Vacuum, 70Min Runtime(ECO), Auto Suction,Mattress vacuum, 1m Flex</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0G5Q6B3S3?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0G64ZJ5MQ?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/511Z9OMUhsL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81ArzYSAbOL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0G5Q6B3S3</t>
+          <t>B0G64ZJ5MQ</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -8768,11 +8722,11 @@
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="19">
-        <v>44</v>
+        <v>3982</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="20">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AG25" s="21">
         <v>0</v>
@@ -8824,7 +8778,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0G64ZJ5MQ</t>
+          <t>B0G8MSDL67</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -8837,23 +8791,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>SMOTURE Cordless Vacuum Cleaner, 55KPa 650W Stick Cordless Vacuum, 70Min Runtime(ECO), Auto Suction,Mattress vacuum, 1m Flex</t>
+          <t>Syntecno Cordless Vacuum Cleaner Stick</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0G64ZJ5MQ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0G8MSDL67?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81ArzYSAbOL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/710qqKJFaxL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0G64ZJ5MQ</t>
+          <t>B0G8MSDL67</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -8874,11 +8828,11 @@
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="19">
-        <v>3982</v>
+        <v>487</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="20">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG26" s="21">
         <v>0</v>
@@ -8930,7 +8884,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0G8MSDL67</t>
+          <t>B0GK6Q2WC4</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -8943,23 +8897,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Syntecno Cordless Vacuum Cleaner Stick</t>
+          <t>Cordless Vacuum Cleaner 600W 50Kpa 70Mins, Stick Vacuum with Hurricane Mode, Anti-Tangle, OLED Touch Screen, Wall-mounted Cha</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0G8MSDL67?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GK6Q2WC4?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/710qqKJFaxL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71ui53zH+hL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0G8MSDL67</t>
+          <t>B0GK6Q2WC4</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -8980,11 +8934,11 @@
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="19">
-        <v>487</v>
+        <v>827</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="20">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AG27" s="21">
         <v>0</v>
@@ -9036,7 +8990,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0GK6Q2WC4</t>
+          <t>B0GPWYRBC5</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -9049,23 +9003,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Cordless Vacuum Cleaner 600W 50Kpa 70Mins, Stick Vacuum with Hurricane Mode, Anti-Tangle, OLED Touch Screen, Wall-mounted Cha</t>
+          <t>Cordless Vacuum Cleaner, 45KPA 6-in-1 Stick Vacuum with Wall Mount &amp; Touch Screen, Up to 60Mins Runtime,Anti Hair Wrap Lightw</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GK6Q2WC4?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GPWYRBC5?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71ui53zH+hL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71hreND61JL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0GK6Q2WC4</t>
+          <t>B0GPWYRBC5</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -9086,11 +9040,11 @@
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="19">
-        <v>827</v>
+        <v>52</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="20">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AG28" s="21">
         <v>0</v>
@@ -9142,7 +9096,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0GPWYRBC5</t>
+          <t>B0GQB23ZPK</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -9155,23 +9109,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Cordless Vacuum Cleaner, 45KPA 6-in-1 Stick Vacuum with Wall Mount &amp; Touch Screen, Up to 60Mins Runtime,Anti Hair Wrap Lightw</t>
+          <t>Zynet DP2 Cordless Vacuum Cleaner with Built-in Dual-Battery System, 48KPa/90Min/600W, LED Display, Telescopic Stick, GreenEy</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GPWYRBC5?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GQB23ZPK?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71hreND61JL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51MFYDSWTOL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0GPWYRBC5</t>
+          <t>B0GQB23ZPK</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -9192,11 +9146,11 @@
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="19">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="20">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG29" s="21">
         <v>0</v>
@@ -9248,7 +9202,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0GQB23ZPK</t>
+          <t>B0GQMGZBWP</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -9261,23 +9215,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Zynet DP2 Cordless Vacuum Cleaner with Built-in Dual-Battery System, 48KPa/90Min/600W, LED Display, Telescopic Stick, GreenEy</t>
+          <t>Cordless Vacuum Cleaner, 550W/45KPA/60min Self-Standing Powerful Vacuum with LED Stylish Display,V-shaped Anti-Tangle Vacuum</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GQB23ZPK?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GQMGZBWP?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51MFYDSWTOL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/612W687g-bL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0GQB23ZPK</t>
+          <t>B0GQMGZBWP</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -9298,11 +9252,11 @@
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="19">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="20">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="AG30" s="21">
         <v>0</v>
@@ -9354,7 +9308,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0GQMGZBWP</t>
+          <t>B0GQYM1LRD</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -9367,23 +9321,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Cordless Vacuum Cleaner, 550W/45KPA/60min Self-Standing Powerful Vacuum with LED Stylish Display,V-shaped Anti-Tangle Vacuum</t>
+          <t>Hoover HF1Max Pet Cordless Vacuum Cleaner Stick, 50min Runtime [XUKF1CP]sRechargeable Baggless Vacuum, 200W motor, Anti-Hai</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GQMGZBWP?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GQYM1LRD?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/612W687g-bL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71Lqsree5-L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0GQMGZBWP</t>
+          <t>B0GQYM1LRD</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -9404,11 +9358,11 @@
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="19">
-        <v>47</v>
+        <v>543</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="20">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AG31" s="21">
         <v>0</v>
@@ -9460,7 +9414,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0GQYM1LRD</t>
+          <t>B0GR48W9G3</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -9473,23 +9427,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Hoover HF1Max Pet Cordless Vacuum Cleaner Stick, 50min Runtime [XUKF1CP]sRechargeable Baggless Vacuum, 200W motor, Anti-Hai</t>
+          <t>Hoover HF3 Core Pet Cordless Vacuum Cleaner Stick, 60min Runtime[HF3CZ10PX]sRechargeable Baggless Vacuum, 340W motor, Anti-</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GQYM1LRD?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GR48W9G3?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71Lqsree5-L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/711XR6tR8LL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0GQYM1LRD</t>
+          <t>B0GR48W9G3</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -9510,11 +9464,11 @@
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="19">
-        <v>543</v>
+        <v>81</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="20">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AG32" s="21">
         <v>0</v>
@@ -9566,7 +9520,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0GR48W9G3</t>
+          <t>B0GR6CYS31</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -9579,23 +9533,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Hoover HF3 Core Pet Cordless Vacuum Cleaner Stick, 60min Runtime[HF3CZ10PX]sRechargeable Baggless Vacuum, 340W motor, Anti-</t>
+          <t>Dyson V10 Konical™ Cordless Vacuum – 150 Air Watts, Powerful Suction, Anti‑Tangle Technology, Detects Invisible Dust, 2‑in‑1</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GR48W9G3?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GR6CYS31?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/711XR6tR8LL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/6148hTag-BL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0GR48W9G3</t>
+          <t>B0GR6CYS31</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -9616,11 +9570,11 @@
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="19">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="20">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG33" s="21">
         <v>0</v>
@@ -9672,7 +9626,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0GR6CYS31</t>
+          <t>B0GS5YJ1NL</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -9685,23 +9639,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Dyson V10 Konical™ Cordless Vacuum – 150 Air Watts, Powerful Suction, Anti‑Tangle Technology, Detects Invisible Dust, 2‑in‑1</t>
+          <t>Powerffy Cordless Vacuum Cleaner, 600W 50KPa Powerful Stick Vacuum for Home, 65 Mins Runtime with Internal Dust Scraper &amp; Aro</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GR6CYS31?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GS5YJ1NL?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/6148hTag-BL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71uqC5qweQL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0GR6CYS31</t>
+          <t>B0GS5YJ1NL</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -9722,11 +9676,11 @@
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34" s="19">
-        <v>63</v>
+        <v>257</v>
       </c>
       <c r="AE34"/>
       <c r="AF34" s="20">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AG34" s="21">
         <v>0</v>
@@ -9778,7 +9732,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0GS5YJ1NL</t>
+          <t>B0GT11SS1N</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -9791,23 +9745,23 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Powerffy Cordless Vacuum Cleaner, 600W 50KPa Powerful Stick Vacuum for Home, 65 Mins Runtime with Internal Dust Scraper &amp; Aro</t>
+          <t>VACTechPro Cordless Vacuum Cleaner, Lightweight Powerful for Pet Hair Homes35KPa/45Mins Stick Vacuum, 6-in-1, with Detachab</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GS5YJ1NL?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GT11SS1N?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71uqC5qweQL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/6191yKufdnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0GS5YJ1NL</t>
+          <t>B0GT11SS1N</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -9828,11 +9782,11 @@
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="19">
-        <v>257</v>
+        <v>5741</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="20">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG35" s="21">
         <v>0</v>
@@ -9884,7 +9838,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0GT11SS1N</t>
+          <t>B0GWQPCM9G</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -9897,23 +9851,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>VACTechPro Cordless Vacuum Cleaner, Lightweight Powerful for Pet Hair Homes35KPa/45Mins Stick Vacuum, 6-in-1, with Detachab</t>
+          <t>80Mins Cordless Vacuum Cleaner, 650W 55Kpa Stick Vacuum Cleaner for HomesSmart LED Touch Display with Auto Mode, 1.8L Dust</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GT11SS1N?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GWQPCM9G?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/6191yKufdnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71hNB8ZvPoL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0GT11SS1N</t>
+          <t>B0GWQPCM9G</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -9934,11 +9888,11 @@
       <c r="AB36"/>
       <c r="AC36"/>
       <c r="AD36" s="19">
-        <v>5741</v>
+        <v>123</v>
       </c>
       <c r="AE36"/>
       <c r="AF36" s="20">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AG36" s="21">
         <v>0</v>
@@ -9990,7 +9944,7 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0GWQPCM9G</t>
+          <t>B0GX6VQ15Y</t>
         </is>
       </c>
       <c r="D37" s="14"/>
@@ -10003,23 +9957,23 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>80Mins Cordless Vacuum Cleaner, 650W 55Kpa Stick Vacuum Cleaner for HomesSmart LED Touch Display with Auto Mode, 1.8L Dust</t>
+          <t>Dyson V8 Cyclone Cordless Vacuum Cleaner, 150 Air Watts, 60 Min Run Times50 Percent More Dirt Removal, Root Cyclone Separat</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GWQPCM9G?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GX6VQ15Y?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71hNB8ZvPoL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/413Kfri1KnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0GWQPCM9G</t>
+          <t>B0GX6VQ15Y</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -10040,11 +9994,11 @@
       <c r="AB37"/>
       <c r="AC37"/>
       <c r="AD37" s="19">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="AE37"/>
       <c r="AF37" s="20">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AG37" s="21">
         <v>0</v>
@@ -10096,7 +10050,7 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0GX6VQ15Y</t>
+          <t>B0GX7C5FGG</t>
         </is>
       </c>
       <c r="D38" s="14"/>
@@ -10109,23 +10063,23 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Dyson V8 Cyclone Cordless Vacuum Cleaner, 150 Air Watts, 60 Min Run Times50 Percent More Dirt Removal, Root Cyclone Separat</t>
+          <t>Shark PowerProPet Cordless Stick VacuumsReveal Technology | IZ381UKT, Electric Blue</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GX6VQ15Y?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GX7C5FGG?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/413Kfri1KnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61fqO9bxc7L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0GX6VQ15Y</t>
+          <t>B0GX7C5FGG</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -10146,7 +10100,7 @@
       <c r="AB38"/>
       <c r="AC38"/>
       <c r="AD38" s="19">
-        <v>55</v>
+        <v>689</v>
       </c>
       <c r="AE38"/>
       <c r="AF38" s="20">
@@ -10202,7 +10156,7 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0GX7C5FGG</t>
+          <t>B0GZW3GVQX</t>
         </is>
       </c>
       <c r="D39" s="14"/>
@@ -10215,23 +10169,23 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Shark PowerProPet Cordless Stick VacuumsReveal Technology | IZ381UKT, Electric Blue</t>
+          <t>Beldray 2 In 1 Stick Vacuum Cleaner, 600W, 1L, HEPA FiltersHandheld Or Stick Use, Washable Filter, 5m Power Cord, Crevice T</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GX7C5FGG?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GZW3GVQX?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61fqO9bxc7L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/518fnu34hgL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0GX7C5FGG</t>
+          <t>B0GZW3GVQX</t>
         </is>
       </c>
       <c r="M39" s="1"/>
@@ -10252,11 +10206,11 @@
       <c r="AB39"/>
       <c r="AC39"/>
       <c r="AD39" s="19">
-        <v>689</v>
+        <v>5486</v>
       </c>
       <c r="AE39"/>
       <c r="AF39" s="20">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AG39" s="21">
         <v>0</v>
@@ -10308,7 +10262,7 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0GZW3GVQX</t>
+          <t>B0H1HRBJGS</t>
         </is>
       </c>
       <c r="D40" s="14"/>
@@ -10321,23 +10275,23 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Beldray 2 In 1 Stick Vacuum Cleaner, 600W, 1L, HEPA FiltersHandheld Or Stick Use, Washable Filter, 5m Power Cord, Crevice T</t>
+          <t>Shark PowerDetect Speed Luxe Collection Clean &amp; Empty Cordless VacuumsAnti-Allergen HEPA Filtration, Up to 60 Min Runtime,</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GZW3GVQX?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H1HRBJGS?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/518fnu34hgL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61YcnDgVTCL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0GZW3GVQX</t>
+          <t>B0H1HRBJGS</t>
         </is>
       </c>
       <c r="M40" s="1"/>
@@ -10358,11 +10312,11 @@
       <c r="AB40"/>
       <c r="AC40"/>
       <c r="AD40" s="19">
-        <v>5486</v>
+        <v>18</v>
       </c>
       <c r="AE40"/>
       <c r="AF40" s="20">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AG40" s="21">
         <v>0</v>
@@ -10414,7 +10368,7 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0H1HRBJGS</t>
+          <t>B0H2JD9BF6</t>
         </is>
       </c>
       <c r="D41" s="14"/>
@@ -10427,23 +10381,23 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Shark PowerDetect Speed Luxe Collection Clean &amp; Empty Cordless VacuumsAnti-Allergen HEPA Filtration, Up to 60 Min Runtime,</t>
+          <t>VACTechPro F02 Ultra Cordless Vacuum Cleaner, 50KPa/600W/70min Stick VacuumsWall-mounted Charging, Removable Battery, Anti-</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H1HRBJGS?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H2JD9BF6?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61YcnDgVTCL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61lKZc+g0IL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0H1HRBJGS</t>
+          <t>B0H2JD9BF6</t>
         </is>
       </c>
       <c r="M41" s="1"/>
@@ -10464,11 +10418,11 @@
       <c r="AB41"/>
       <c r="AC41"/>
       <c r="AD41" s="19">
-        <v>18</v>
+        <v>215</v>
       </c>
       <c r="AE41"/>
       <c r="AF41" s="20">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AG41" s="21">
         <v>0</v>
@@ -10520,7 +10474,7 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0H2JD9BF6</t>
+          <t>B0H2QFKJCY</t>
         </is>
       </c>
       <c r="D42" s="14"/>
@@ -10533,23 +10487,23 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>VACTechPro F02 Ultra Cordless Vacuum Cleaner, 50KPa/600W/70min Stick VacuumsWall-mounted Charging, Removable Battery, Anti-</t>
+          <t>Cordless Vacuum Cleaner Stick Vacuums - Powerful Lightweight Electric Brooms Upright Handheld Wireless Bagless Battery Rechar</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H2JD9BF6?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H2QFKJCY?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61lKZc+g0IL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71HGMrdoD5L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0H2JD9BF6</t>
+          <t>B0H2QFKJCY</t>
         </is>
       </c>
       <c r="M42" s="1"/>
@@ -10570,11 +10524,11 @@
       <c r="AB42"/>
       <c r="AC42"/>
       <c r="AD42" s="19">
-        <v>215</v>
+        <v>21</v>
       </c>
       <c r="AE42"/>
       <c r="AF42" s="20">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AG42" s="21">
         <v>0</v>
@@ -10626,7 +10580,7 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0H2QFKJCY</t>
+          <t>B0H2TW76WH</t>
         </is>
       </c>
       <c r="D43" s="14"/>
@@ -10639,23 +10593,23 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Cordless Vacuum Cleaner Stick Vacuums - Powerful Lightweight Electric Brooms Upright Handheld Wireless Bagless Battery Rechar</t>
+          <t>SunSare Cordless Vacuum Cleaner, 55KPa 650W 70Mins Stick Vacuum with Aromatherapy, 1.8L One-Pull Dust Cup, Green Headlights,</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H2QFKJCY?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H2TW76WH?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71HGMrdoD5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71L1ozsIULL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0H2QFKJCY</t>
+          <t>B0H2TW76WH</t>
         </is>
       </c>
       <c r="M43" s="1"/>
@@ -10676,11 +10630,11 @@
       <c r="AB43"/>
       <c r="AC43"/>
       <c r="AD43" s="19">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="AE43"/>
       <c r="AF43" s="20">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG43" s="21">
         <v>0</v>
@@ -10732,7 +10686,7 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0H2TW76WH</t>
+          <t>B0H3N8MK58</t>
         </is>
       </c>
       <c r="D44" s="14"/>
@@ -10745,23 +10699,23 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>SunSare Cordless Vacuum Cleaner, 55KPa 650W 70Mins Stick Vacuum with Aromatherapy, 1.8L One-Pull Dust Cup, Green Headlights,</t>
+          <t>L12E Cordless Vacuum Cleaner, 46KPa/400W Powerful Stick Vacuum, 1L DustbinsHandheld Cordless Vacuum, Removable Battery, Wal</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H2TW76WH?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H3N8MK58?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71L1ozsIULL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61Y41LdD4xL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0H2TW76WH</t>
+          <t>B0H3N8MK58</t>
         </is>
       </c>
       <c r="M44" s="1"/>
@@ -10782,11 +10736,11 @@
       <c r="AB44"/>
       <c r="AC44"/>
       <c r="AD44" s="19">
-        <v>154</v>
+        <v>4</v>
       </c>
       <c r="AE44"/>
       <c r="AF44" s="20">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AG44" s="21">
         <v>0</v>
@@ -10838,7 +10792,7 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0H3N8MK58</t>
+          <t>B0H4LPTHCX</t>
         </is>
       </c>
       <c r="D45" s="14"/>
@@ -10851,23 +10805,23 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>L12E Cordless Vacuum Cleaner, 46KPa/400W Powerful Stick Vacuum, 1L DustbinsHandheld Cordless Vacuum, Removable Battery, Wal</t>
+          <t>ASKGIFT Cordless Vacuum Cleaner, Lightweight Stick &amp; Handheld VacuumsFor Pet Hair, Carpets, and Hard Floors | Rechargeable</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H3N8MK58?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H4LPTHCX?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61Y41LdD4xL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61e71x43A1L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0H3N8MK58</t>
+          <t>B0H4LPTHCX</t>
         </is>
       </c>
       <c r="M45" s="1"/>
@@ -10888,7 +10842,7 @@
       <c r="AB45"/>
       <c r="AC45"/>
       <c r="AD45" s="19">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="AE45"/>
       <c r="AF45" s="20">
@@ -10944,7 +10898,7 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0H4LPTHCX</t>
+          <t>B0H5VX44CH</t>
         </is>
       </c>
       <c r="D46" s="14"/>
@@ -10957,23 +10911,23 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>ASKGIFT Cordless Vacuum Cleaner, Lightweight Stick &amp; Handheld VacuumsFor Pet Hair, Carpets, and Hard Floors | Rechargeable</t>
+          <t>SIXPAD S80 Cordless Vacuum Cleaner, 45KPa Stick Vacuum Cleaner with Smart Dust Detection, 550W Brushless Motor, 55 Mins Runti</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H4LPTHCX?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H5VX44CH?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61e71x43A1L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61e35TxdjOL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0H4LPTHCX</t>
+          <t>B0H5VX44CH</t>
         </is>
       </c>
       <c r="M46" s="1"/>
@@ -10994,11 +10948,11 @@
       <c r="AB46"/>
       <c r="AC46"/>
       <c r="AD46" s="19">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="AE46"/>
       <c r="AF46" s="20">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AG46" s="21">
         <v>0</v>
@@ -11050,7 +11004,7 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0H5VX44CH</t>
+          <t>B0H5WGMNRB</t>
         </is>
       </c>
       <c r="D47" s="14"/>
@@ -11063,23 +11017,23 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>SIXPAD S80 Cordless Vacuum Cleaner, 45KPa Stick Vacuum Cleaner with Smart Dust Detection, 550W Brushless Motor, 55 Mins Runti</t>
+          <t>Vexilar Corded Vacuum Cleaner 60KPa/600W,Self-Standing,1.5L Large Dustbins6-in-1 Corded Stick Vacuum Cleaner with 6-Stage F</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H5VX44CH?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H5WGMNRB?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61e35TxdjOL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71OrHXVoREL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0H5VX44CH</t>
+          <t>B0H5WGMNRB</t>
         </is>
       </c>
       <c r="M47" s="1"/>
@@ -11095,16 +11049,18 @@
       <c r="W47" s="15"/>
       <c r="X47" s="15"/>
       <c r="Y47"/>
-      <c r="Z47" s="4"/>
+      <c r="Z47" s="4">
+        <v>66.66</v>
+      </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47"/>
       <c r="AD47" s="19">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="AE47"/>
       <c r="AF47" s="20">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG47" s="21">
         <v>0</v>
@@ -11156,7 +11112,7 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0H5WGMNRB</t>
+          <t>B0H6X8GZSW</t>
         </is>
       </c>
       <c r="D48" s="14"/>
@@ -11169,23 +11125,23 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Vexilar Corded Vacuum Cleaner 60KPa/600W,Self-Standing,1.5L Large Dustbins6-in-1 Corded Stick Vacuum Cleaner with 6-Stage F</t>
+          <t>Vexilar Cordless Vacuum Cleaner V12, 50Kpa Powerful Suction,50Min RuntimesHandheld Vacuum Cleaner Cordless with GreenEye Te</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H5WGMNRB?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H6X8GZSW?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71OrHXVoREL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71pLW5nM4GL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0H5WGMNRB</t>
+          <t>B0H6X8GZSW</t>
         </is>
       </c>
       <c r="M48" s="1"/>
@@ -11201,18 +11157,16 @@
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
       <c r="Y48"/>
-      <c r="Z48" s="4">
-        <v>66.66</v>
-      </c>
+      <c r="Z48" s="4"/>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48"/>
       <c r="AD48" s="19">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="AE48"/>
       <c r="AF48" s="20">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AG48" s="21">
         <v>0</v>
@@ -11264,7 +11218,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0H6X8GZSW</t>
+          <t>B0H87Q3599</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -11277,23 +11231,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Vexilar Cordless Vacuum Cleaner V12, 50Kpa Powerful Suction,50Min RuntimesHandheld Vacuum Cleaner Cordless with GreenEye Te</t>
+          <t>INTETURE Cordless Vacuum Cleaner, 600W 50KPA Stick Vacuum with Touch Screen, Up to 65 Mins Runtime, Powerful Vacuum with Rech</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H6X8GZSW?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H87Q3599?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71pLW5nM4GL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71pSgeQa8jL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0H6X8GZSW</t>
+          <t>B0H87Q3599</t>
         </is>
       </c>
       <c r="M49" s="1"/>
@@ -11314,11 +11268,11 @@
       <c r="AB49"/>
       <c r="AC49"/>
       <c r="AD49" s="19">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="AE49"/>
       <c r="AF49" s="20">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AG49" s="21">
         <v>0</v>
@@ -11370,7 +11324,7 @@
       <c r="B50" s="13"/>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>B0H87Q3599</t>
+          <t>B0HCZGTHV2</t>
         </is>
       </c>
       <c r="D50" s="14"/>
@@ -11383,23 +11337,23 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>INTETURE Cordless Vacuum Cleaner, 600W 50KPA Stick Vacuum with Touch Screen, Up to 65 Mins Runtime, Powerful Vacuum with Rech</t>
+          <t>Cordless Vacuum Cleaner 650W 55KPA, 70Mins Battery Cordless Stick VacuumsLED Touch Screen・Auto Mode・180° Foldable Wand + 1M</t>
         </is>
       </c>
       <c r="I50" s="14"/>
       <c r="J50" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H87Q3599?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0HCZGTHV2?psc=1</t>
         </is>
       </c>
       <c r="K50" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71pSgeQa8jL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71amryCWm8L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>B0H87Q3599</t>
+          <t>B0HCZGTHV2</t>
         </is>
       </c>
       <c r="M50" s="1"/>
@@ -11420,11 +11374,11 @@
       <c r="AB50"/>
       <c r="AC50"/>
       <c r="AD50" s="19">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="AE50"/>
       <c r="AF50" s="20">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AG50" s="21">
         <v>0</v>
@@ -11468,112 +11422,6 @@
       <c r="BP50"/>
       <c r="BQ50" s="22"/>
       <c r="BR50"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HCZGTHV2</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Cordless Vacuum Cleaner 650W 55KPA, 70Mins Battery Cordless Stick VacuumsLED Touch Screen・Auto Mode・180° Foldable Wand + 1M</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0HCZGTHV2?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71amryCWm8L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HCZGTHV2</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="19">
-        <v>34</v>
-      </c>
-      <c r="AE51"/>
-      <c r="AF51" s="20">
-        <v>5</v>
-      </c>
-      <c r="AG51" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="22"/>
-      <c r="BL51"/>
-      <c r="BM51" s="22"/>
-      <c r="BN51"/>
-      <c r="BO51" s="22"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="22"/>
-      <c r="BR51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11669,168 +11517,163 @@
     <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.co.uk/dp/B0F5X43L2H?psc=1"/>
     <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61K-FBySP+L._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.co.uk/dp/B0F5X43L2H"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.co.uk/dp/B0FCGB8FPQ"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61y78uO9VYL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.co.uk/dp/B0F9YPP9C3"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.co.uk/dp/B0FCGB8FPQ"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.co.uk/dp/B0FCGB8FPQ?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61TKqdXibWL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.co.uk/dp/B0FCGB8FPQ"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.co.uk/dp/B0FPMR4Q3T"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.co.uk/dp/B0FCGB8FPQ?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61TKqdXibWL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.co.uk/dp/B0FCGB8FPQ"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.co.uk/dp/B0FPMR4Q3T"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.co.uk/dp/B0FPMR4Q3T?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/610Cokti-gL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.co.uk/dp/B0FPMR4Q3T"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.co.uk/dp/B0FT2LTJRF"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.co.uk/dp/B0FPMR4Q3T?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/610Cokti-gL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.co.uk/dp/B0FPMR4Q3T"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.co.uk/dp/B0FT2LTJRF"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.co.uk/dp/B0FT2LTJRF?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71amryCWm8L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.co.uk/dp/B0FT2LTJRF"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.co.uk/dp/B0G2LVVRMJ"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.co.uk/dp/B0FT2LTJRF?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71amryCWm8L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.co.uk/dp/B0FT2LTJRF"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.co.uk/dp/B0G2LVVRMJ"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.co.uk/dp/B0G2LVVRMJ?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gB5S-38uL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.co.uk/dp/B0G2LVVRMJ"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.co.uk/dp/B0G5Q6B3S3"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.co.uk/dp/B0G2LVVRMJ?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71gB5S-38uL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.co.uk/dp/B0G2LVVRMJ"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.co.uk/dp/B0G5Q6B3S3"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.co.uk/dp/B0G5Q6B3S3?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511Z9OMUhsL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.co.uk/dp/B0G5Q6B3S3"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.co.uk/dp/B0G64ZJ5MQ"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.co.uk/dp/B0G5Q6B3S3?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/511Z9OMUhsL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.co.uk/dp/B0G5Q6B3S3"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.co.uk/dp/B0G64ZJ5MQ"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.co.uk/dp/B0G64ZJ5MQ?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81ArzYSAbOL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.co.uk/dp/B0G64ZJ5MQ"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.co.uk/dp/B0G8MSDL67"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.co.uk/dp/B0G64ZJ5MQ?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81ArzYSAbOL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.co.uk/dp/B0G64ZJ5MQ"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.co.uk/dp/B0G8MSDL67"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.co.uk/dp/B0G8MSDL67?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/710qqKJFaxL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.co.uk/dp/B0G8MSDL67"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.co.uk/dp/B0GK6Q2WC4"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.co.uk/dp/B0G8MSDL67?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/710qqKJFaxL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.co.uk/dp/B0G8MSDL67"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.co.uk/dp/B0GK6Q2WC4"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.co.uk/dp/B0GK6Q2WC4?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ui53zH+hL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.co.uk/dp/B0GK6Q2WC4"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.co.uk/dp/B0GPWYRBC5"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.co.uk/dp/B0GK6Q2WC4?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ui53zH+hL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.co.uk/dp/B0GK6Q2WC4"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.co.uk/dp/B0GPWYRBC5"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.co.uk/dp/B0GPWYRBC5?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71hreND61JL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.co.uk/dp/B0GPWYRBC5"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.co.uk/dp/B0GQB23ZPK"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.co.uk/dp/B0GPWYRBC5?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71hreND61JL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.co.uk/dp/B0GPWYRBC5"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.co.uk/dp/B0GQB23ZPK"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.co.uk/dp/B0GQB23ZPK?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51MFYDSWTOL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.co.uk/dp/B0GQB23ZPK"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.co.uk/dp/B0GQB23ZPK?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51MFYDSWTOL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.co.uk/dp/B0GQB23ZPK"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/612W687g-bL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.co.uk/dp/B0GQYM1LRD"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/612W687g-bL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.co.uk/dp/B0GQMGZBWP"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.co.uk/dp/B0GQYM1LRD"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.co.uk/dp/B0GQYM1LRD?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Lqsree5-L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.co.uk/dp/B0GQYM1LRD"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.co.uk/dp/B0GR48W9G3"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.co.uk/dp/B0GQYM1LRD?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Lqsree5-L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.co.uk/dp/B0GQYM1LRD"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.co.uk/dp/B0GR48W9G3"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.co.uk/dp/B0GR48W9G3?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/711XR6tR8LL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.co.uk/dp/B0GR48W9G3"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.co.uk/dp/B0GR6CYS31"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.co.uk/dp/B0GR48W9G3?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/711XR6tR8LL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.co.uk/dp/B0GR48W9G3"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.co.uk/dp/B0GR6CYS31"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.co.uk/dp/B0GR6CYS31?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6148hTag-BL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.co.uk/dp/B0GR6CYS31"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.co.uk/dp/B0GS5YJ1NL"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.co.uk/dp/B0GR6CYS31?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6148hTag-BL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.co.uk/dp/B0GR6CYS31"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.co.uk/dp/B0GS5YJ1NL"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.co.uk/dp/B0GS5YJ1NL?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71uqC5qweQL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.co.uk/dp/B0GS5YJ1NL"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.co.uk/dp/B0GT11SS1N"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.co.uk/dp/B0GS5YJ1NL?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71uqC5qweQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.co.uk/dp/B0GS5YJ1NL"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.co.uk/dp/B0GT11SS1N"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.co.uk/dp/B0GT11SS1N?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6191yKufdnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.co.uk/dp/B0GT11SS1N"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.co.uk/dp/B0GWQPCM9G"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.co.uk/dp/B0GT11SS1N?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/6191yKufdnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.co.uk/dp/B0GT11SS1N"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.co.uk/dp/B0GWQPCM9G"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.co.uk/dp/B0GWQPCM9G?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71hNB8ZvPoL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.co.uk/dp/B0GWQPCM9G"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.co.uk/dp/B0GX6VQ15Y"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.co.uk/dp/B0GWQPCM9G?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71hNB8ZvPoL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.co.uk/dp/B0GWQPCM9G"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.co.uk/dp/B0GX6VQ15Y"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.co.uk/dp/B0GX6VQ15Y?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/413Kfri1KnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.co.uk/dp/B0GX6VQ15Y"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.co.uk/dp/B0GX7C5FGG"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.co.uk/dp/B0GX6VQ15Y?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/413Kfri1KnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.co.uk/dp/B0GX6VQ15Y"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.co.uk/dp/B0GX7C5FGG"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.co.uk/dp/B0GX7C5FGG?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61fqO9bxc7L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.co.uk/dp/B0GX7C5FGG"/>
+    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.co.uk/dp/B0GZW3GVQX"/>
     <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.co.uk/dp/B0GX7C5FGG?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61fqO9bxc7L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.co.uk/dp/B0GX7C5FGG"/>
-    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.co.uk/dp/B0GZW3GVQX"/>
+    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.co.uk/dp/B0GZW3GVQX?psc=1"/>
+    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/518fnu34hgL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.co.uk/dp/B0GZW3GVQX"/>
+    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.co.uk/dp/B0H1HRBJGS"/>
     <hyperlink ref="G40" r:id="rId192" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.co.uk/dp/B0GZW3GVQX?psc=1"/>
-    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/518fnu34hgL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.co.uk/dp/B0GZW3GVQX"/>
-    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.co.uk/dp/B0H1HRBJGS"/>
+    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.co.uk/dp/B0H1HRBJGS?psc=1"/>
+    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61YcnDgVTCL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.co.uk/dp/B0H1HRBJGS"/>
+    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.co.uk/dp/B0H2JD9BF6"/>
     <hyperlink ref="G41" r:id="rId197" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.co.uk/dp/B0H1HRBJGS?psc=1"/>
-    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61YcnDgVTCL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.co.uk/dp/B0H1HRBJGS"/>
-    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.co.uk/dp/B0H2JD9BF6"/>
+    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.co.uk/dp/B0H2JD9BF6?psc=1"/>
+    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61lKZc+g0IL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.co.uk/dp/B0H2JD9BF6"/>
+    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.co.uk/dp/B0H2QFKJCY"/>
     <hyperlink ref="G42" r:id="rId202" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.co.uk/dp/B0H2JD9BF6?psc=1"/>
-    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61lKZc+g0IL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.co.uk/dp/B0H2JD9BF6"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.co.uk/dp/B0H2QFKJCY"/>
+    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.co.uk/dp/B0H2QFKJCY?psc=1"/>
+    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71HGMrdoD5L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.co.uk/dp/B0H2QFKJCY"/>
+    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.co.uk/dp/B0H2TW76WH"/>
     <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.co.uk/dp/B0H2QFKJCY?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71HGMrdoD5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.co.uk/dp/B0H2QFKJCY"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.co.uk/dp/B0H2TW76WH"/>
+    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.co.uk/dp/B0H2TW76WH?psc=1"/>
+    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71L1ozsIULL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.co.uk/dp/B0H2TW76WH"/>
+    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58"/>
     <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.co.uk/dp/B0H2TW76WH?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71L1ozsIULL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.co.uk/dp/B0H2TW76WH"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58"/>
+    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58?psc=1"/>
+    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Y41LdD4xL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58"/>
+    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.co.uk/dp/B0H4LPTHCX"/>
     <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Y41LdD4xL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.co.uk/dp/B0H3N8MK58"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.co.uk/dp/B0H4LPTHCX"/>
+    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.co.uk/dp/B0H4LPTHCX?psc=1"/>
+    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61e71x43A1L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.co.uk/dp/B0H4LPTHCX"/>
+    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.co.uk/dp/B0H5VX44CH"/>
     <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.co.uk/dp/B0H4LPTHCX?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61e71x43A1L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.co.uk/dp/B0H4LPTHCX"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.co.uk/dp/B0H5VX44CH"/>
+    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.co.uk/dp/B0H5VX44CH?psc=1"/>
+    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61e35TxdjOL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.co.uk/dp/B0H5VX44CH"/>
+    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.co.uk/dp/B0H5WGMNRB"/>
     <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.co.uk/dp/B0H5VX44CH?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61e35TxdjOL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.co.uk/dp/B0H5VX44CH"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.co.uk/dp/B0H5WGMNRB"/>
+    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.co.uk/dp/B0H5WGMNRB?psc=1"/>
+    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OrHXVoREL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.co.uk/dp/B0H5WGMNRB"/>
+    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.co.uk/dp/B0H6X8GZSW"/>
     <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.co.uk/dp/B0H5WGMNRB?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71OrHXVoREL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.co.uk/dp/B0H5WGMNRB"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.co.uk/dp/B0H6X8GZSW"/>
+    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.co.uk/dp/B0H6X8GZSW?psc=1"/>
+    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pLW5nM4GL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.co.uk/dp/B0H6X8GZSW"/>
+    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.co.uk/dp/B0H87Q3599"/>
     <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.co.uk/dp/B0H6X8GZSW?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pLW5nM4GL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.co.uk/dp/B0H6X8GZSW"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.co.uk/dp/B0H87Q3599"/>
+    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.co.uk/dp/B0H87Q3599?psc=1"/>
+    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pSgeQa8jL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.co.uk/dp/B0H87Q3599"/>
+    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.co.uk/dp/B0HCZGTHV2"/>
     <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.co.uk/dp/B0H87Q3599?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pSgeQa8jL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.co.uk/dp/B0H87Q3599"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.co.uk/dp/B0HCZGTHV2"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.co.uk/dp/B0HCZGTHV2?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71amryCWm8L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.co.uk/dp/B0HCZGTHV2"/>
+    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.co.uk/dp/B0HCZGTHV2?psc=1"/>
+    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71amryCWm8L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.co.uk/dp/B0HCZGTHV2"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId246"/>
 </worksheet>
 </file>
 
